--- a/99_economic/Z.economic_pulse_monthly/pce_pi_detail.xlsx
+++ b/99_economic/Z.economic_pulse_monthly/pce_pi_detail.xlsx
@@ -1448,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>117.766</v>
+        <v>117.77</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>-0.003663313564412518</v>
+        <v>-0.003629472330561212</v>
       </c>
       <c r="L20" t="n">
         <v>24</v>
@@ -2420,7 +2420,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>122.805</v>
+        <v>122.747</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>0.0364165752384169</v>
+        <v>0.0359270824542155</v>
       </c>
       <c r="L39" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="40">
@@ -5336,7 +5336,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>122.991</v>
+        <v>122.992</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         </is>
       </c>
       <c r="K96" t="n">
-        <v>0.02217364926073984</v>
+        <v>0.0221819602237312</v>
       </c>
       <c r="L96" t="n">
         <v>48</v>
@@ -7280,7 +7280,7 @@
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>92.435</v>
+        <v>92.434</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="K134" t="n">
-        <v>0.003789935495080776</v>
+        <v>0.003779076081054544</v>
       </c>
       <c r="L134" t="n">
         <v>30</v>
@@ -10196,7 +10196,7 @@
         <v>0</v>
       </c>
       <c r="I191" t="n">
-        <v>100.711</v>
+        <v>100.715</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         </is>
       </c>
       <c r="K191" t="n">
-        <v>-0.002604630895082005</v>
+        <v>-0.00256501673698184</v>
       </c>
       <c r="L191" t="n">
         <v>25</v>
@@ -11168,7 +11168,7 @@
         <v>0</v>
       </c>
       <c r="I210" t="n">
-        <v>131.293</v>
+        <v>131.295</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         </is>
       </c>
       <c r="K210" t="n">
-        <v>0.04164418774396239</v>
+        <v>0.04166005521881244</v>
       </c>
       <c r="L210" t="n">
         <v>72</v>
@@ -12140,7 +12140,7 @@
         <v>0</v>
       </c>
       <c r="I229" t="n">
-        <v>131.2</v>
+        <v>131.202</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -12148,10 +12148,10 @@
         </is>
       </c>
       <c r="K229" t="n">
-        <v>0.03533719480437481</v>
+        <v>0.03535297738356413</v>
       </c>
       <c r="L229" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="230">
@@ -14084,7 +14084,7 @@
         <v>0</v>
       </c>
       <c r="I267" t="n">
-        <v>140.673</v>
+        <v>140.64</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
@@ -14092,10 +14092,10 @@
         </is>
       </c>
       <c r="K267" t="n">
-        <v>0.03603623508616871</v>
+        <v>0.03579319487406085</v>
       </c>
       <c r="L267" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="268">
@@ -15056,7 +15056,7 @@
         <v>0</v>
       </c>
       <c r="I286" t="n">
-        <v>111.95</v>
+        <v>111.951</v>
       </c>
       <c r="J286" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         </is>
       </c>
       <c r="K286" t="n">
-        <v>-0.02562361829164272</v>
+        <v>-0.02561491461695142</v>
       </c>
       <c r="L286" t="n">
         <v>10</v>
@@ -16028,7 +16028,7 @@
         <v>0</v>
       </c>
       <c r="I305" t="n">
-        <v>128.176</v>
+        <v>128.219</v>
       </c>
       <c r="J305" t="inlineStr">
         <is>
@@ -16036,7 +16036,7 @@
         </is>
       </c>
       <c r="K305" t="n">
-        <v>0.1071894408596576</v>
+        <v>0.1075608765883196</v>
       </c>
       <c r="L305" t="n">
         <v>92</v>
@@ -17000,7 +17000,7 @@
         <v>0</v>
       </c>
       <c r="I324" t="n">
-        <v>142.579</v>
+        <v>142.952</v>
       </c>
       <c r="J324" t="inlineStr">
         <is>
@@ -17008,10 +17008,10 @@
         </is>
       </c>
       <c r="K324" t="n">
-        <v>0.05467201230878493</v>
+        <v>0.05743113294079372</v>
       </c>
       <c r="L324" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="325">
@@ -17983,7 +17983,7 @@
         <v>0.03835066761986039</v>
       </c>
       <c r="L343" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="344">
@@ -19916,7 +19916,7 @@
         <v>0</v>
       </c>
       <c r="I381" t="n">
-        <v>100.171</v>
+        <v>100.212</v>
       </c>
       <c r="J381" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         </is>
       </c>
       <c r="K381" t="n">
-        <v>-0.02342698929553289</v>
+        <v>-0.02302727786768577</v>
       </c>
       <c r="L381" t="n">
         <v>11</v>
@@ -20888,7 +20888,7 @@
         <v>0</v>
       </c>
       <c r="I400" t="n">
-        <v>146.27</v>
+        <v>146.3</v>
       </c>
       <c r="J400" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="K400" t="n">
-        <v>-0.09679212078174682</v>
+        <v>-0.09660687270369561</v>
       </c>
       <c r="L400" t="n">
         <v>2</v>
@@ -21860,7 +21860,7 @@
         <v>0</v>
       </c>
       <c r="I419" t="n">
-        <v>128.155</v>
+        <v>128.156</v>
       </c>
       <c r="J419" t="inlineStr">
         <is>
@@ -21868,7 +21868,7 @@
         </is>
       </c>
       <c r="K419" t="n">
-        <v>0.02640599721283365</v>
+        <v>0.02641400631116952</v>
       </c>
       <c r="L419" t="n">
         <v>52</v>
@@ -22832,7 +22832,7 @@
         <v>0</v>
       </c>
       <c r="I438" t="n">
-        <v>103.982</v>
+        <v>103.983</v>
       </c>
       <c r="J438" t="inlineStr">
         <is>
@@ -22840,7 +22840,7 @@
         </is>
       </c>
       <c r="K438" t="n">
-        <v>0.008232088662212922</v>
+        <v>0.008241784879718494</v>
       </c>
       <c r="L438" t="n">
         <v>33</v>
@@ -23804,7 +23804,7 @@
         <v>0</v>
       </c>
       <c r="I457" t="n">
-        <v>114.397</v>
+        <v>114.398</v>
       </c>
       <c r="J457" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         </is>
       </c>
       <c r="K457" t="n">
-        <v>-0.007461585847280405</v>
+        <v>-0.007452909584667378</v>
       </c>
       <c r="L457" t="n">
         <v>23</v>
@@ -24776,7 +24776,7 @@
         <v>0</v>
       </c>
       <c r="I476" t="n">
-        <v>130.789</v>
+        <v>130.793</v>
       </c>
       <c r="J476" t="inlineStr">
         <is>
@@ -24784,7 +24784,7 @@
         </is>
       </c>
       <c r="K476" t="n">
-        <v>0.01082008516952748</v>
+        <v>0.01085099969858327</v>
       </c>
       <c r="L476" t="n">
         <v>35</v>
@@ -25748,7 +25748,7 @@
         <v>0</v>
       </c>
       <c r="I495" t="n">
-        <v>104.542</v>
+        <v>104.538</v>
       </c>
       <c r="J495" t="inlineStr">
         <is>
@@ -25756,7 +25756,7 @@
         </is>
       </c>
       <c r="K495" t="n">
-        <v>-0.02126145693876214</v>
+        <v>-0.02129890556392955</v>
       </c>
       <c r="L495" t="n">
         <v>14</v>
@@ -27692,7 +27692,7 @@
         <v>0</v>
       </c>
       <c r="I533" t="n">
-        <v>114.144</v>
+        <v>114.143</v>
       </c>
       <c r="J533" t="inlineStr">
         <is>
@@ -27700,7 +27700,7 @@
         </is>
       </c>
       <c r="K533" t="n">
-        <v>0.01717208622579469</v>
+        <v>0.01716317492002095</v>
       </c>
       <c r="L533" t="n">
         <v>43</v>
@@ -28664,7 +28664,7 @@
         <v>0</v>
       </c>
       <c r="I552" t="n">
-        <v>142.219</v>
+        <v>142.22</v>
       </c>
       <c r="J552" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         </is>
       </c>
       <c r="K552" t="n">
-        <v>0.04092895254964235</v>
+        <v>0.04093627174716552</v>
       </c>
       <c r="L552" t="n">
         <v>70</v>
@@ -29636,7 +29636,7 @@
         <v>0</v>
       </c>
       <c r="I571" t="n">
-        <v>116.027</v>
+        <v>116.045</v>
       </c>
       <c r="J571" t="inlineStr">
         <is>
@@ -29644,10 +29644,10 @@
         </is>
       </c>
       <c r="K571" t="n">
-        <v>0.03304070657786951</v>
+        <v>0.0332009686954664</v>
       </c>
       <c r="L571" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="572">
@@ -30608,7 +30608,7 @@
         <v>0</v>
       </c>
       <c r="I590" t="n">
-        <v>115.236</v>
+        <v>115.235</v>
       </c>
       <c r="J590" t="inlineStr">
         <is>
@@ -30616,7 +30616,7 @@
         </is>
       </c>
       <c r="K590" t="n">
-        <v>-0.02608960219061374</v>
+        <v>-0.02609805363285245</v>
       </c>
       <c r="L590" t="n">
         <v>9</v>
@@ -31580,7 +31580,7 @@
         <v>0</v>
       </c>
       <c r="I609" t="n">
-        <v>122.726</v>
+        <v>122.468</v>
       </c>
       <c r="J609" t="inlineStr">
         <is>
@@ -31588,10 +31588,10 @@
         </is>
       </c>
       <c r="K609" t="n">
-        <v>0.03464090307460133</v>
+        <v>0.0324658354198808</v>
       </c>
       <c r="L609" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="610">
@@ -33524,7 +33524,7 @@
         <v>0</v>
       </c>
       <c r="I647" t="n">
-        <v>121.613</v>
+        <v>121.589</v>
       </c>
       <c r="J647" t="inlineStr">
         <is>
@@ -33532,10 +33532,10 @@
         </is>
       </c>
       <c r="K647" t="n">
-        <v>0.03361437386323063</v>
+        <v>0.03341039283346636</v>
       </c>
       <c r="L647" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="648">
@@ -34496,7 +34496,7 @@
         <v>0</v>
       </c>
       <c r="I666" t="n">
-        <v>152.685</v>
+        <v>153.003</v>
       </c>
       <c r="J666" t="inlineStr">
         <is>
@@ -34504,10 +34504,10 @@
         </is>
       </c>
       <c r="K666" t="n">
-        <v>0.02844498929018879</v>
+        <v>0.03058695154315583</v>
       </c>
       <c r="L666" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="667">
@@ -35468,7 +35468,7 @@
         <v>0</v>
       </c>
       <c r="I685" t="n">
-        <v>121.778</v>
+        <v>121.951</v>
       </c>
       <c r="J685" t="inlineStr">
         <is>
@@ -35476,10 +35476,10 @@
         </is>
       </c>
       <c r="K685" t="n">
-        <v>0.04458740778864301</v>
+        <v>0.04607136730142392</v>
       </c>
       <c r="L685" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="686">
@@ -36440,7 +36440,7 @@
         <v>0</v>
       </c>
       <c r="I704" t="n">
-        <v>110.303</v>
+        <v>110.301</v>
       </c>
       <c r="J704" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         </is>
       </c>
       <c r="K704" t="n">
-        <v>0.02947407718512296</v>
+        <v>0.02945541089178216</v>
       </c>
       <c r="L704" t="n">
         <v>55</v>
@@ -37412,7 +37412,7 @@
         <v>0</v>
       </c>
       <c r="I723" t="n">
-        <v>112.297</v>
+        <v>112.296</v>
       </c>
       <c r="J723" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         </is>
       </c>
       <c r="K723" t="n">
-        <v>0.020214041718148</v>
+        <v>0.02020495675557821</v>
       </c>
       <c r="L723" t="n">
         <v>47</v>
@@ -38384,7 +38384,7 @@
         <v>0</v>
       </c>
       <c r="I742" t="n">
-        <v>126.867</v>
+        <v>126.809</v>
       </c>
       <c r="J742" t="inlineStr">
         <is>
@@ -38392,7 +38392,7 @@
         </is>
       </c>
       <c r="K742" t="n">
-        <v>0.04688699096422821</v>
+        <v>0.04640838387589219</v>
       </c>
       <c r="L742" t="n">
         <v>78</v>
@@ -40328,7 +40328,7 @@
         <v>0</v>
       </c>
       <c r="I780" t="n">
-        <v>109.273</v>
+        <v>109.274</v>
       </c>
       <c r="J780" t="inlineStr">
         <is>
@@ -40336,7 +40336,7 @@
         </is>
       </c>
       <c r="K780" t="n">
-        <v>0.004255123609962164</v>
+        <v>0.004264313941733322</v>
       </c>
       <c r="L780" t="n">
         <v>31</v>
@@ -44216,7 +44216,7 @@
         <v>0</v>
       </c>
       <c r="I856" t="n">
-        <v>139.595</v>
+        <v>139.585</v>
       </c>
       <c r="J856" t="inlineStr">
         <is>
@@ -44224,7 +44224,7 @@
         </is>
       </c>
       <c r="K856" t="n">
-        <v>0.02893807723208686</v>
+        <v>0.02886436842609585</v>
       </c>
       <c r="L856" t="n">
         <v>54</v>
@@ -45188,7 +45188,7 @@
         <v>0</v>
       </c>
       <c r="I875" t="n">
-        <v>119.549</v>
+        <v>119.55</v>
       </c>
       <c r="J875" t="inlineStr">
         <is>
@@ -45196,7 +45196,7 @@
         </is>
       </c>
       <c r="K875" t="n">
-        <v>0.000100387327772955</v>
+        <v>0.0001087529384207198</v>
       </c>
       <c r="L875" t="n">
         <v>27</v>
@@ -46160,7 +46160,7 @@
         <v>0</v>
       </c>
       <c r="I894" t="n">
-        <v>128.852</v>
+        <v>128.849</v>
       </c>
       <c r="J894" t="inlineStr">
         <is>
@@ -46168,7 +46168,7 @@
         </is>
       </c>
       <c r="K894" t="n">
-        <v>0.0516641909208142</v>
+        <v>0.05163970552227348</v>
       </c>
       <c r="L894" t="n">
         <v>83</v>
@@ -47132,7 +47132,7 @@
         <v>0</v>
       </c>
       <c r="I913" t="n">
-        <v>132.148</v>
+        <v>132.144</v>
       </c>
       <c r="J913" t="inlineStr">
         <is>
@@ -47140,10 +47140,10 @@
         </is>
       </c>
       <c r="K913" t="n">
-        <v>0.0326160001250253</v>
+        <v>0.03258474377607956</v>
       </c>
       <c r="L913" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="914">
@@ -48104,7 +48104,7 @@
         <v>0</v>
       </c>
       <c r="I932" t="n">
-        <v>120.478</v>
+        <v>120.477</v>
       </c>
       <c r="J932" t="inlineStr">
         <is>
@@ -48112,7 +48112,7 @@
         </is>
       </c>
       <c r="K932" t="n">
-        <v>-0.01176258284664355</v>
+        <v>-0.01177078548461186</v>
       </c>
       <c r="L932" t="n">
         <v>19</v>
@@ -50048,7 +50048,7 @@
         <v>0</v>
       </c>
       <c r="I970" t="n">
-        <v>129.57</v>
+        <v>127.827</v>
       </c>
       <c r="J970" t="inlineStr">
         <is>
@@ -50056,10 +50056,10 @@
         </is>
       </c>
       <c r="K970" t="n">
-        <v>0.04083993380781759</v>
+        <v>0.0268383593335797</v>
       </c>
       <c r="L970" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
     </row>
     <row r="971">
@@ -51020,7 +51020,7 @@
         <v>0</v>
       </c>
       <c r="I989" t="n">
-        <v>106.458</v>
+        <v>106.459</v>
       </c>
       <c r="J989" t="inlineStr">
         <is>
@@ -51028,7 +51028,7 @@
         </is>
       </c>
       <c r="K989" t="n">
-        <v>0.0003664759112564919</v>
+        <v>0.000375872729493798</v>
       </c>
       <c r="L989" t="n">
         <v>28</v>
@@ -51992,7 +51992,7 @@
         <v>0</v>
       </c>
       <c r="I1008" t="n">
-        <v>133.628</v>
+        <v>134.058</v>
       </c>
       <c r="J1008" t="inlineStr">
         <is>
@@ -52000,7 +52000,7 @@
         </is>
       </c>
       <c r="K1008" t="n">
-        <v>0.08598270593589485</v>
+        <v>0.08947727716013265</v>
       </c>
       <c r="L1008" t="n">
         <v>91</v>
@@ -54908,7 +54908,7 @@
         <v>0</v>
       </c>
       <c r="I1065" t="n">
-        <v>112.749</v>
+        <v>112.761</v>
       </c>
       <c r="J1065" t="inlineStr">
         <is>
@@ -54916,7 +54916,7 @@
         </is>
       </c>
       <c r="K1065" t="n">
-        <v>0.01686523146853758</v>
+        <v>0.01697345755282775</v>
       </c>
       <c r="L1065" t="n">
         <v>41</v>
@@ -57824,7 +57824,7 @@
         <v>0</v>
       </c>
       <c r="I1122" t="n">
-        <v>123.734</v>
+        <v>123.747</v>
       </c>
       <c r="J1122" t="inlineStr">
         <is>
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="K1122" t="n">
-        <v>0.02273873188795106</v>
+        <v>0.0228461850011985</v>
       </c>
       <c r="L1122" t="n">
         <v>50</v>
@@ -58796,7 +58796,7 @@
         <v>0</v>
       </c>
       <c r="I1141" t="n">
-        <v>142.041</v>
+        <v>142.046</v>
       </c>
       <c r="J1141" t="inlineStr">
         <is>
@@ -58804,7 +58804,7 @@
         </is>
       </c>
       <c r="K1141" t="n">
-        <v>0.05206983134707532</v>
+        <v>0.05210686536652576</v>
       </c>
       <c r="L1141" t="n">
         <v>85</v>
@@ -60740,7 +60740,7 @@
         <v>0</v>
       </c>
       <c r="I1179" t="n">
-        <v>109.762</v>
+        <v>109.785</v>
       </c>
       <c r="J1179" t="inlineStr">
         <is>
@@ -60748,10 +60748,10 @@
         </is>
       </c>
       <c r="K1179" t="n">
-        <v>0.01554375381654682</v>
+        <v>0.01575655520808272</v>
       </c>
       <c r="L1179" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1180">
@@ -62684,7 +62684,7 @@
         <v>0</v>
       </c>
       <c r="I1217" t="n">
-        <v>112.539</v>
+        <v>112.54</v>
       </c>
       <c r="J1217" t="inlineStr">
         <is>
@@ -62692,7 +62692,7 @@
         </is>
       </c>
       <c r="K1217" t="n">
-        <v>0.01104123618722497</v>
+        <v>0.01105022010601031</v>
       </c>
       <c r="L1217" t="n">
         <v>36</v>
@@ -63656,7 +63656,7 @@
         <v>0</v>
       </c>
       <c r="I1236" t="n">
-        <v>131.899</v>
+        <v>131.913</v>
       </c>
       <c r="J1236" t="inlineStr">
         <is>
@@ -63664,7 +63664,7 @@
         </is>
       </c>
       <c r="K1236" t="n">
-        <v>0.04248205873984379</v>
+        <v>0.04259270968353834</v>
       </c>
       <c r="L1236" t="n">
         <v>73</v>
@@ -64628,7 +64628,7 @@
         <v>0</v>
       </c>
       <c r="I1255" t="n">
-        <v>142.953</v>
+        <v>142.956</v>
       </c>
       <c r="J1255" t="inlineStr">
         <is>
@@ -64636,10 +64636,10 @@
         </is>
       </c>
       <c r="K1255" t="n">
-        <v>0.05550222983549413</v>
+        <v>0.05552438051921182</v>
       </c>
       <c r="L1255" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="1256">
@@ -65600,7 +65600,7 @@
         <v>0</v>
       </c>
       <c r="I1274" t="n">
-        <v>117.227</v>
+        <v>117.194</v>
       </c>
       <c r="J1274" t="inlineStr">
         <is>
@@ -65608,10 +65608,10 @@
         </is>
       </c>
       <c r="K1274" t="n">
-        <v>0.01557667483907865</v>
+        <v>0.01529078481144253</v>
       </c>
       <c r="L1274" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1275">
@@ -66572,7 +66572,7 @@
         <v>0</v>
       </c>
       <c r="I1293" t="n">
-        <v>104.397</v>
+        <v>104.4</v>
       </c>
       <c r="J1293" t="inlineStr">
         <is>
@@ -66580,7 +66580,7 @@
         </is>
       </c>
       <c r="K1293" t="n">
-        <v>0.01292388298646485</v>
+        <v>0.01295299083102908</v>
       </c>
       <c r="L1293" t="n">
         <v>37</v>
@@ -68516,7 +68516,7 @@
         <v>0</v>
       </c>
       <c r="I1331" t="n">
-        <v>121.847</v>
+        <v>121.784</v>
       </c>
       <c r="J1331" t="inlineStr">
         <is>
@@ -68524,10 +68524,10 @@
         </is>
       </c>
       <c r="K1331" t="n">
-        <v>0.03688102592904596</v>
+        <v>0.03634491503067738</v>
       </c>
       <c r="L1331" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="1332">
@@ -69488,7 +69488,7 @@
         <v>0</v>
       </c>
       <c r="I1350" t="n">
-        <v>128.296</v>
+        <v>128.315</v>
       </c>
       <c r="J1350" t="inlineStr">
         <is>
@@ -69496,10 +69496,10 @@
         </is>
       </c>
       <c r="K1350" t="n">
-        <v>0.03718794463846842</v>
+        <v>0.03734154701849701</v>
       </c>
       <c r="L1350" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="1351">
@@ -70460,7 +70460,7 @@
         <v>0</v>
       </c>
       <c r="I1369" t="n">
-        <v>133.223</v>
+        <v>133.204</v>
       </c>
       <c r="J1369" t="inlineStr">
         <is>
@@ -70468,7 +70468,7 @@
         </is>
       </c>
       <c r="K1369" t="n">
-        <v>0.04779544775297695</v>
+        <v>0.04764601324461637</v>
       </c>
       <c r="L1369" t="n">
         <v>79</v>
@@ -74348,7 +74348,7 @@
         <v>0</v>
       </c>
       <c r="I1445" t="n">
-        <v>80.96299999999999</v>
+        <v>80.964</v>
       </c>
       <c r="J1445" t="inlineStr">
         <is>
@@ -74356,7 +74356,7 @@
         </is>
       </c>
       <c r="K1445" t="n">
-        <v>-0.01581493727511429</v>
+        <v>-0.01580278128950696</v>
       </c>
       <c r="L1445" t="n">
         <v>17</v>
@@ -75320,7 +75320,7 @@
         <v>0</v>
       </c>
       <c r="I1464" t="n">
-        <v>116.243</v>
+        <v>116.241</v>
       </c>
       <c r="J1464" t="inlineStr">
         <is>
@@ -75328,7 +75328,7 @@
         </is>
       </c>
       <c r="K1464" t="n">
-        <v>0.02313975390356804</v>
+        <v>0.02312215043920629</v>
       </c>
       <c r="L1464" t="n">
         <v>51</v>
@@ -78236,7 +78236,7 @@
         <v>0</v>
       </c>
       <c r="I1521" t="n">
-        <v>130.606</v>
+        <v>131.515</v>
       </c>
       <c r="J1521" t="inlineStr">
         <is>
@@ -78244,7 +78244,7 @@
         </is>
       </c>
       <c r="K1521" t="n">
-        <v>0.06084555090768795</v>
+        <v>0.06822889168663449</v>
       </c>
       <c r="L1521" t="n">
         <v>89</v>
@@ -80180,7 +80180,7 @@
         <v>0</v>
       </c>
       <c r="I1559" t="n">
-        <v>122.704</v>
+        <v>122.703</v>
       </c>
       <c r="J1559" t="inlineStr">
         <is>
@@ -80188,7 +80188,7 @@
         </is>
       </c>
       <c r="K1559" t="n">
-        <v>-0.0268152436848158</v>
+        <v>-0.02682317484236818</v>
       </c>
       <c r="L1559" t="n">
         <v>8</v>
@@ -81152,7 +81152,7 @@
         <v>0</v>
       </c>
       <c r="I1578" t="n">
-        <v>87.627</v>
+        <v>87.629</v>
       </c>
       <c r="J1578" t="inlineStr">
         <is>
@@ -81160,7 +81160,7 @@
         </is>
       </c>
       <c r="K1578" t="n">
-        <v>-0.07602518004576286</v>
+        <v>-0.07600409123021601</v>
       </c>
       <c r="L1578" t="n">
         <v>5</v>
@@ -82124,7 +82124,7 @@
         <v>0</v>
       </c>
       <c r="I1597" t="n">
-        <v>131.756</v>
+        <v>131.759</v>
       </c>
       <c r="J1597" t="inlineStr">
         <is>
@@ -82132,10 +82132,10 @@
         </is>
       </c>
       <c r="K1597" t="n">
-        <v>0.03815999936964687</v>
+        <v>0.0381836376100162</v>
       </c>
       <c r="L1597" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1598">
@@ -83096,7 +83096,7 @@
         <v>0</v>
       </c>
       <c r="I1616" t="n">
-        <v>72.651</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="J1616" t="inlineStr">
         <is>
@@ -83104,7 +83104,7 @@
         </is>
       </c>
       <c r="K1616" t="n">
-        <v>-0.0108242790621681</v>
+        <v>-0.01083789450752926</v>
       </c>
       <c r="L1616" t="n">
         <v>20</v>
@@ -84068,7 +84068,7 @@
         <v>0</v>
       </c>
       <c r="I1635" t="n">
-        <v>112.543</v>
+        <v>112.544</v>
       </c>
       <c r="J1635" t="inlineStr">
         <is>
@@ -84076,7 +84076,7 @@
         </is>
       </c>
       <c r="K1635" t="n">
-        <v>0.01699770472248829</v>
+        <v>0.01700674124812473</v>
       </c>
       <c r="L1635" t="n">
         <v>42</v>
@@ -85040,7 +85040,7 @@
         <v>0</v>
       </c>
       <c r="I1654" t="n">
-        <v>145.234</v>
+        <v>145.226</v>
       </c>
       <c r="J1654" t="inlineStr">
         <is>
@@ -85048,10 +85048,10 @@
         </is>
       </c>
       <c r="K1654" t="n">
-        <v>0.04517976913555377</v>
+        <v>0.04512219695443176</v>
       </c>
       <c r="L1654" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1655">
@@ -86012,7 +86012,7 @@
         <v>0</v>
       </c>
       <c r="I1673" t="n">
-        <v>98.402</v>
+        <v>98.411</v>
       </c>
       <c r="J1673" t="inlineStr">
         <is>
@@ -86020,7 +86020,7 @@
         </is>
       </c>
       <c r="K1673" t="n">
-        <v>-0.05591480379929004</v>
+        <v>-0.05582845629857047</v>
       </c>
       <c r="L1673" t="n">
         <v>6</v>
@@ -86984,7 +86984,7 @@
         <v>0</v>
       </c>
       <c r="I1692" t="n">
-        <v>100.4</v>
+        <v>100.401</v>
       </c>
       <c r="J1692" t="inlineStr">
         <is>
@@ -86992,7 +86992,7 @@
         </is>
       </c>
       <c r="K1692" t="n">
-        <v>0.01354761856690012</v>
+        <v>0.01355771366270253</v>
       </c>
       <c r="L1692" t="n">
         <v>38</v>
@@ -88939,7 +88939,7 @@
         <v>0.04481093049459872</v>
       </c>
       <c r="L1730" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="1731">
